--- a/practice/answers/q041.xlsx
+++ b/practice/answers/q041.xlsx
@@ -102412,7 +102412,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Question 41 — Average Yield of Two Varieties by Year</t>
+          <t>Question 40 — Average Yield of Two Varieties by Year</t>
         </is>
       </c>
     </row>
